--- a/data/trans_camb/IP19C03-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C03-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 14,83</t>
+          <t>-14,54; 15,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 25,12</t>
+          <t>-14,2; 22,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,75; 25,79</t>
+          <t>-19,01; 26,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 29,05</t>
+          <t>-3,21; 27,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 33,25</t>
+          <t>-1,37; 33,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,39; 11,96</t>
+          <t>-22,45; 13,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 16,59</t>
+          <t>-3,83; 16,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 22,58</t>
+          <t>-4,42; 22,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,73; 14,34</t>
+          <t>-15,51; 14,96</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-43,52; 86,78</t>
+          <t>-44,4; 98,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-45,68; 135,46</t>
+          <t>-49,17; 135,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-67,56; 168,5</t>
+          <t>-68,28; 166,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 209,68</t>
+          <t>-13,35; 190,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 240,59</t>
+          <t>-4,82; 242,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-83,35; 89,93</t>
+          <t>-83,71; 90,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 93,53</t>
+          <t>-13,66; 90,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 118,09</t>
+          <t>-13,75; 122,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-58,93; 83,02</t>
+          <t>-59,96; 76,81</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 4,57</t>
+          <t>-8,18; 4,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 1,48</t>
+          <t>-10,54; 1,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,75; -0,03</t>
+          <t>-12,19; 0,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 8,81</t>
+          <t>-1,91; 9,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 7,56</t>
+          <t>-4,01; 6,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 6,9</t>
+          <t>-4,34; 7,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 5,47</t>
+          <t>-3,21; 5,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 2,8</t>
+          <t>-5,72; 2,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 1,76</t>
+          <t>-5,84; 1,92</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-29,46; 22,54</t>
+          <t>-30,8; 22,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-40,02; 6,58</t>
+          <t>-40,09; 9,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-43,57; 1,35</t>
+          <t>-45,14; 0,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 62,26</t>
+          <t>-9,78; 66,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,7; 53,08</t>
+          <t>-20,38; 48,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,81; 49,87</t>
+          <t>-22,21; 51,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 30,86</t>
+          <t>-14,75; 31,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,38; 15,38</t>
+          <t>-25,86; 13,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-30,61; 9,29</t>
+          <t>-27,14; 11,55</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 13,14</t>
+          <t>-3,54; 14,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 5,81</t>
+          <t>-9,07; 4,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 13,43</t>
+          <t>-1,91; 13,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,38; -0,62</t>
+          <t>-18,23; -1,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 3,91</t>
+          <t>-14,41; 4,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,17; 4,29</t>
+          <t>-13,76; 4,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 3,23</t>
+          <t>-7,81; 3,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 2,31</t>
+          <t>-8,98; 1,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 6,89</t>
+          <t>-5,65; 6,7</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-30,86; 228,86</t>
+          <t>-31,07; 250,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-66,86; 107,16</t>
+          <t>-67,3; 97,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-24,57; 227,81</t>
+          <t>-17,67; 229,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-78,3; 9,65</t>
+          <t>-81,26; -4,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-65,85; 34,09</t>
+          <t>-63,88; 41,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,65; 36,49</t>
+          <t>-64,12; 35,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-50,82; 30,73</t>
+          <t>-49,1; 38,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-57,68; 25,36</t>
+          <t>-57,52; 18,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-32,93; 72,91</t>
+          <t>-34,76; 71,22</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 5,29</t>
+          <t>-5,18; 4,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 1,02</t>
+          <t>-8,46; 0,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 1,33</t>
+          <t>-7,82; 1,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 6,51</t>
+          <t>-2,76; 6,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 4,66</t>
+          <t>-4,12; 5,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 3,86</t>
+          <t>-5,36; 3,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 4,12</t>
+          <t>-2,45; 4,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 1,81</t>
+          <t>-4,86; 2,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 0,9</t>
+          <t>-5,62; 1,28</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-22,88; 29,39</t>
+          <t>-22,41; 23,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-35,96; 6,31</t>
+          <t>-36,81; 3,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-33,46; 6,82</t>
+          <t>-34,09; 10,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 43,07</t>
+          <t>-14,58; 42,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-18,81; 29,7</t>
+          <t>-21,09; 32,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-28,74; 25,27</t>
+          <t>-27,76; 24,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 24,06</t>
+          <t>-12,37; 25,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-22,96; 10,4</t>
+          <t>-23,22; 12,21</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-27,14; 5,49</t>
+          <t>-27,12; 7,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C03-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C03-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,54; 15,98</t>
+          <t>-13,87; 13,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 22,14</t>
+          <t>-13,8; 22,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,01; 26,99</t>
+          <t>-17,95; 27,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 27,98</t>
+          <t>-3,14; 26,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 33,72</t>
+          <t>-1,55; 34,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,45; 13,01</t>
+          <t>-24,39; 9,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 16,91</t>
+          <t>-4,75; 17,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 22,75</t>
+          <t>-2,93; 22,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,51; 14,96</t>
+          <t>-15,86; 14,45</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-44,4; 98,16</t>
+          <t>-44,17; 76,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-49,17; 135,89</t>
+          <t>-46,93; 123,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-68,28; 166,17</t>
+          <t>-66,78; 136,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 190,65</t>
+          <t>-11,46; 182,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 242,01</t>
+          <t>-7,13; 237,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-83,71; 90,35</t>
+          <t>-85,48; 63,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 90,89</t>
+          <t>-16,85; 95,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 122,44</t>
+          <t>-11,47; 126,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-59,96; 76,81</t>
+          <t>-60,13; 75,04</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 4,54</t>
+          <t>-7,97; 4,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 1,85</t>
+          <t>-10,9; 1,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 0,13</t>
+          <t>-12,27; -0,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 9,28</t>
+          <t>-1,95; 9,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 6,92</t>
+          <t>-4,75; 6,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 7,37</t>
+          <t>-4,38; 7,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 5,65</t>
+          <t>-2,91; 5,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 2,51</t>
+          <t>-5,29; 2,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 1,92</t>
+          <t>-6,24; 2,01</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-30,8; 22,29</t>
+          <t>-30,24; 22,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-40,09; 9,56</t>
+          <t>-39,51; 7,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-45,14; 0,94</t>
+          <t>-46,07; -0,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 66,04</t>
+          <t>-11,15; 68,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,38; 48,98</t>
+          <t>-23,64; 44,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,21; 51,9</t>
+          <t>-23,23; 50,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,75; 31,76</t>
+          <t>-13,46; 30,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,86; 13,71</t>
+          <t>-24,17; 14,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-27,14; 11,55</t>
+          <t>-28,58; 10,89</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 14,07</t>
+          <t>-3,42; 14,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 4,9</t>
+          <t>-8,9; 5,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 13,5</t>
+          <t>-1,97; 14,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,23; -1,53</t>
+          <t>-17,63; 0,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,41; 4,14</t>
+          <t>-14,5; 3,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 4,32</t>
+          <t>-13,71; 3,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 3,97</t>
+          <t>-7,99; 4,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 1,75</t>
+          <t>-9,79; 2,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 6,7</t>
+          <t>-5,55; 6,26</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,07; 250,57</t>
+          <t>-28,97; 238,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-67,3; 97,38</t>
+          <t>-67,61; 79,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 229,26</t>
+          <t>-18,89; 247,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-81,26; -4,39</t>
+          <t>-80,92; 6,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-63,88; 41,95</t>
+          <t>-63,12; 37,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,12; 35,04</t>
+          <t>-64,17; 33,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-49,1; 38,54</t>
+          <t>-48,87; 46,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-57,52; 18,48</t>
+          <t>-57,33; 29,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-34,76; 71,22</t>
+          <t>-34,74; 62,71</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 4,42</t>
+          <t>-5,39; 4,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 0,81</t>
+          <t>-8,42; 0,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 1,89</t>
+          <t>-8,06; 1,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 6,56</t>
+          <t>-2,7; 7,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 5,02</t>
+          <t>-3,96; 5,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 3,73</t>
+          <t>-6,16; 3,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 4,37</t>
+          <t>-2,59; 3,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 2,08</t>
+          <t>-4,9; 1,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 1,28</t>
+          <t>-5,36; 1,14</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-22,41; 23,74</t>
+          <t>-23,18; 23,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,81; 3,98</t>
+          <t>-36,93; 4,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-34,09; 10,73</t>
+          <t>-35,53; 9,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,58; 42,17</t>
+          <t>-13,5; 46,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-21,09; 32,55</t>
+          <t>-19,48; 35,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-27,76; 24,09</t>
+          <t>-30,57; 21,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 25,28</t>
+          <t>-12,0; 22,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-23,22; 12,21</t>
+          <t>-23,47; 9,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-27,12; 7,02</t>
+          <t>-25,74; 6,74</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C03-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C03-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12,5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14,96</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-5,86</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,09</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>3,61</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,6</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12,5</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>14,96</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-6,74</t>
+          <t>-7,91</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-3,39</t>
+          <t>-6,93</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 13,6</t>
+          <t>-2,47; 29,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 22,18</t>
+          <t>-3,72; 33,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,95; 27,51</t>
+          <t>-22,05; 13,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 26,9</t>
+          <t>-13,42; 14,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 34,89</t>
+          <t>-13,02; 25,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,39; 9,78</t>
+          <t>-23,17; 9,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 17,65</t>
+          <t>-3,98; 16,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 22,83</t>
+          <t>-4,12; 22,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 14,45</t>
+          <t>-17,98; 5,69</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>56,86%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68,06%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-26,67%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>14,62%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-2,45%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>56,86%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>68,06%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-30,66%</t>
+          <t>-32,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-14,5%</t>
+          <t>-29,63%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-44,17; 76,65</t>
+          <t>-9,12; 209,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-46,93; 123,76</t>
+          <t>-13,33; 240,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-66,78; 136,21</t>
+          <t>-82,16; 96,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 182,61</t>
+          <t>-43,52; 86,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 237,39</t>
+          <t>-45,68; 135,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-85,48; 63,42</t>
+          <t>-74,38; 60,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,85; 95,55</t>
+          <t>-13,57; 93,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 126,26</t>
+          <t>-12,72; 118,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-60,13; 75,04</t>
+          <t>-66,29; 31,93</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,68</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,38</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,76</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-1,57</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-4,49</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-5,94</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,68</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,38</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,08</t>
+          <t>-5,82</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,28</t>
+          <t>-2,41</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 4,61</t>
+          <t>-2,31; 8,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 1,42</t>
+          <t>-4,14; 7,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,27; -0,32</t>
+          <t>-4,93; 6,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 9,96</t>
+          <t>-7,74; 4,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 6,4</t>
+          <t>-11,02; 1,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 7,33</t>
+          <t>-11,83; 0,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 5,56</t>
+          <t>-2,92; 5,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 2,65</t>
+          <t>-5,76; 2,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 2,01</t>
+          <t>-6,91; 1,42</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>21,64%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8,11%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4,46%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-6,66%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-18,99%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-25,12%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>21,64%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,11%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>-24,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-11,31%</t>
+          <t>-11,95%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-30,24; 22,55</t>
+          <t>-11,17; 62,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,51; 7,18</t>
+          <t>-21,7; 53,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-46,07; -0,91</t>
+          <t>-25,55; 47,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 68,26</t>
+          <t>-29,46; 22,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,64; 44,84</t>
+          <t>-40,02; 6,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,23; 50,32</t>
+          <t>-43,27; 0,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,46; 30,75</t>
+          <t>-13,09; 30,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,17; 14,4</t>
+          <t>-26,38; 15,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-28,58; 10,89</t>
+          <t>-31,06; 8,02</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-9,12</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-5,14</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-5,79</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>5,14</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-1,62</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5,83</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-9,12</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-5,14</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-4,64</t>
+          <t>5,36</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>-0,36</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 14,08</t>
+          <t>-17,38; -0,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 5,49</t>
+          <t>-13,78; 3,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 14,35</t>
+          <t>-15,69; 2,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,63; 0,45</t>
+          <t>-3,98; 13,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 3,47</t>
+          <t>-8,71; 5,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 3,74</t>
+          <t>-3,24; 12,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 4,19</t>
+          <t>-8,8; 3,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 2,7</t>
+          <t>-9,57; 2,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 6,26</t>
+          <t>-6,18; 5,57</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-54,41%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-30,63%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-34,5%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>53,69%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-16,88%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>60,92%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-54,41%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-30,63%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-27,69%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>-2,71%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-28,97; 238,06</t>
+          <t>-78,3; 9,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-67,61; 79,17</t>
+          <t>-65,85; 34,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-18,89; 247,56</t>
+          <t>-67,43; 24,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-80,92; 6,37</t>
+          <t>-30,86; 228,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-63,12; 37,66</t>
+          <t>-66,86; 107,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,17; 33,39</t>
+          <t>-26,78; 229,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-48,87; 46,98</t>
+          <t>-50,82; 30,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-57,33; 29,97</t>
+          <t>-57,68; 25,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-34,74; 62,71</t>
+          <t>-36,65; 60,41</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,85</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,65</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-1,74</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-0,1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-3,75</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,15</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,85</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,65</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,28</t>
+          <t>-3,76</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,26</t>
+          <t>-2,77</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 4,39</t>
+          <t>-3,23; 6,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 0,92</t>
+          <t>-3,74; 4,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 1,81</t>
+          <t>-6,02; 3,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 7,02</t>
+          <t>-5,0; 5,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 5,37</t>
+          <t>-8,38; 1,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 3,24</t>
+          <t>-8,51; 0,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 3,94</t>
+          <t>-2,32; 4,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 1,66</t>
+          <t>-4,76; 1,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 1,14</t>
+          <t>-6,04; 0,48</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>10,57%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-9,93%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-0,47%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-18,06%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-15,17%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>10,57%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-7,31%</t>
+          <t>-18,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-11,83%</t>
+          <t>-14,49%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-23,18; 23,69</t>
+          <t>-16,11; 43,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,93; 4,65</t>
+          <t>-18,81; 29,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-35,53; 9,96</t>
+          <t>-30,54; 22,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 46,38</t>
+          <t>-22,88; 29,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,48; 35,17</t>
+          <t>-35,96; 6,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-30,57; 21,27</t>
+          <t>-36,3; 3,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 22,23</t>
+          <t>-11,1; 24,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-23,47; 9,37</t>
+          <t>-22,96; 10,4</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-25,74; 6,74</t>
+          <t>-29,06; 3,04</t>
         </is>
       </c>
     </row>
